--- a/infrastructure_forms/010_facility_modernization_progress_survey--infrastructure_forms.xlsx
+++ b/infrastructure_forms/010_facility_modernization_progress_survey--infrastructure_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,46 +515,54 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>main_page</t>
+          <t>phase_1_status</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Introduction</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Phase 1 Status</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please describe the current status of Phase 1.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>phase_2_start_date</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Phase 2 Start Date</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Approximate date when Phase 2 started.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +574,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>site_name</t>
+          <t>phase_2_status</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Site</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Phase 2 Status</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Describe the current status of Phase 2.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +601,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>phase_1</t>
+          <t>phase_3_status</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Phase 3 Status</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Describe the current status of Phase 3.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +628,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>phase_1_start_date</t>
+          <t>phase_3_start_date</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Start date</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Phase 3 Start Date</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Approximate date when Phase 3 started.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +655,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>phase_2</t>
+          <t>phase_4_status</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phase 2</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Phase 4 Status</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Describe the current status of Phase 4.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +682,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>phase_2_start_date</t>
+          <t>phase_4_start_date</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Start date</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Phase 4 Start Date</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Approximate date when Phase 4 started.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +709,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>phase_3</t>
+          <t>phase_5_status</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phase 3</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Phase 5 Status</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Describe the current status of Phase 5.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,18 +736,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>phase_3_start_date</t>
+          <t>phase_5_start_date</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Start date</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Phase 5 Start Date</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Approximate date when Phase 5 started.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +763,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>phase_4</t>
+          <t>phase_6_status</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phase 4</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Phase 6 Status</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Describe the current status of Phase 6.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +790,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>phase_4_start_date</t>
+          <t>phase_6_start_date</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Start date</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Phase 6 Start Date</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Approximate date when Phase 6 started.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +817,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>phase_5</t>
+          <t>phase_7_status</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phase 5</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Phase 7 Status</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Describe the current status of Phase 7.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,18 +844,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>phase_5_start_date</t>
+          <t>phase_7_start_date</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Start date</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Phase 7 Start Date</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Approximate date when Phase 7 started.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,15 +871,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>phase_6</t>
+          <t>phase_8_status</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Phase 6</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Phase 8 Status</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Describe the status of Phase 8.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -842,15 +898,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>phase_6_start_date</t>
+          <t>phase_8_start_date</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Start date</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Phase 8 Start Date</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>If Phase 8 has started, please enter the date.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -860,69 +920,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>phase_7</t>
+          <t>phase_8_status_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phase 7</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Phase 8 Status 2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>If Phase 8 has progressed, please describe its status.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>phase_8</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Phase 8</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>phase_8_status</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -940,7 +958,7 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
@@ -965,7 +983,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>phase_8_status_choices</t>
+          <t>phase_8_status_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -982,7 +1000,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>phase_8_status_choices</t>
+          <t>phase_8_status_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
